--- a/parser/data/xlsx/preprocesses_1.xlsx
+++ b/parser/data/xlsx/preprocesses_1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:56:42.785383</t>
+          <t>2026-02-25T17:23:29.614902</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_c24603f2.csv</t>
+          <t>data_preprocessed_1_0b0ba787.csv</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c24603f2.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocesses_1.xlsx
+++ b/parser/data/xlsx/preprocesses_1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T17:23:29.614902</t>
+          <t>2026-02-25T18:04:18.518344</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_0b0ba787.csv</t>
+          <t>data_preprocessed_1_7ee3ce34.csv</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocesses_1.xlsx
+++ b/parser/data/xlsx/preprocesses_1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T18:04:18.518344</t>
+          <t>2026-02-26T13:48:49.861360</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_7ee3ce34.csv</t>
+          <t>data_preprocessed_1_ca031a75.csv</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocesses_1.xlsx
+++ b/parser/data/xlsx/preprocesses_1.xlsx
@@ -419,7 +419,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="103" customWidth="1" min="2" max="2"/>
+    <col width="131" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T13:48:49.861360</t>
+          <t>2026-02-26T14:46:10.641136</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>7abc486a8f2944fab510c38389cbf6f4</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\churn\data.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\7abc486a8f2944fab510c38389cbf6f4.csv</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_ca031a75.csv</t>
+          <t>7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348.csv</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocesses_1.xlsx
+++ b/parser/data/xlsx/preprocesses_1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T14:46:10.641136</t>
+          <t>2026-02-26T14:55:24.572348</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7abc486a8f2944fab510c38389cbf6f4</t>
+          <t>5a6b5300428640cbaae38090de224504</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\7abc486a8f2944fab510c38389cbf6f4.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\5a6b5300428640cbaae38090de224504.csv</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348.csv</t>
+          <t>5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4.csv</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocesses_1.xlsx
+++ b/parser/data/xlsx/preprocesses_1.xlsx
@@ -10,6 +10,12 @@
     <sheet name="record_1_metadata" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="record_1_steps" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="record_1_deferred" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="record_2_metadata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="record_2_steps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="record_2_deferred" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="record_3_metadata" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="record_3_steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="record_3_deferred" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1172,1522 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="113" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:08:38.913962</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dataset_path</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\traffic_violations_100k\data.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>output_file_name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>data_preprocessed_1_c13340b5.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>output_file_path</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c13340b5.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>identifier columns</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>drop_columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>impute_numeric_median</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>impute_categorical_mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>impute_categorical_mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dl_state</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>impute_categorical_mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>skew stabilization</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>log_transform</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text_vectorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text_vectorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>accident</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>belts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>personal_injury</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>property_damage</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>commercial_license</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hazmat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>commercial_vehicle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>work_zone</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vehicletype</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>make</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>contributed_to_accident</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>driver_state</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dl_state</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="131" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:13:08.114431</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>42d1e5bfc1a9434c8980fd2b57f3f8d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dataset_path</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\42d1e5bfc1a9434c8980fd2b57f3f8d8.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>output_file_name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>output_file_path</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>identifier columns</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>drop_columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>impute_numeric_median</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>impute_categorical_mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>impute_categorical_mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dl_state</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>structural missing handling</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>impute_categorical_mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>skew stabilization</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>executed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>log_transform</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text_vectorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text_vectorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>accident</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>belts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>personal_injury</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>property_damage</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>commercial_license</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hazmat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>commercial_vehicle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>work_zone</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vehicletype</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>make</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>contributed_to_accident</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>driver_state</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dl_state</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>